--- a/playwright poc/data/excel/tests/Users_Test_Cases.xlsx
+++ b/playwright poc/data/excel/tests/Users_Test_Cases.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -76,7 +76,7 @@
     <t>User should be created and visible in list</t>
   </si>
   <si>
-    <t xml:space="preserve">{"firstName":"Alice","lastName":"Doe","email":"alice@example.cm","phone":"1234567890","reason":"Checkup","state":"AZ","dobYear":"1990","dobMonth":"January","dobDay":"15"}
+    <t xml:space="preserve">{"firstName":"Alice","lastName":"Doe","email":"alice@exccample.cm","phone":"1234567890","reason":"Checkup","state":"AZ","dobYear":"1990","dobMonth":"January","dobDay":"15"}
 </t>
   </si>
   <si>
@@ -84,6 +84,16 @@
   </si>
   <si>
     <t>create</t>
+  </si>
+  <si>
+    <t>TC-USER-DELETE-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{"firstName":"Alice"}
+</t>
+  </si>
+  <si>
+    <t>delete</t>
   </si>
 </sst>
 </file>
@@ -91,13 +101,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -133,25 +149,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,62 +465,62 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="4" width="147.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="31.5" customFormat="1" s="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="195" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -538,7 +548,7 @@
       <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
@@ -546,6 +556,44 @@
       </c>
       <c r="L2" s="2" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="60" customFormat="1" s="1">
+      <c r="A3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/playwright poc/data/excel/tests/Users_Test_Cases.xlsx
+++ b/playwright poc/data/excel/tests/Users_Test_Cases.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -87,6 +87,15 @@
   </si>
   <si>
     <t>TC-USER-DELETE-02</t>
+  </si>
+  <si>
+    <t>delete user</t>
+  </si>
+  <si>
+    <t>delete the user name</t>
+  </si>
+  <si>
+    <t>user name is supposed to be deleted</t>
   </si>
   <si>
     <t xml:space="preserve">{"firstName":"Alice"}
@@ -101,19 +110,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -149,15 +152,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -468,21 +468,21 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="4" width="147.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="3" width="147.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="31.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -510,7 +510,7 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="57" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="60" customFormat="1" s="1">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -548,7 +548,7 @@
       <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
@@ -558,42 +558,42 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="60" customFormat="1" s="1">
-      <c r="A3" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="46.5" customFormat="1" s="1">
+      <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="3" t="s">
+      <c r="H3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>25</v>
+      <c r="L3" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
